--- a/Files/sridevi-satta-penal-chart.xlsx
+++ b/Files/sridevi-satta-penal-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$446</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$447</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2390,6 +2390,12 @@
   </x:si>
   <x:si>
     <x:t>14/09/2026 to 20/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026 to 27/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2845,7 +2851,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V446"/>
+  <x:dimension ref="A1:V447"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -33135,53 +33141,121 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H446" s="3" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="I446" s="3" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="J446" s="3" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="K446" s="3" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="L446" s="3" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="M446" s="3" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="N446" s="3" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="O446" s="3" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="P446" s="3" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="Q446" s="3" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="R446" s="3" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="S446" s="3" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="T446" s="3" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="U446" s="3" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="V446" s="3" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" spans="1:22">
+      <x:c r="A447" s="3" t="s">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="B447" s="3" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="C447" s="3" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D447" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E447" s="3" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F447" s="3" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G447" s="3" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H447" s="3" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="I447" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J447" s="3" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="K447" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="L447" s="3" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="M447" s="3" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="N447" s="3" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="O447" s="3" t="s">
+        <x:v>792</x:v>
+      </x:c>
+      <x:c r="P447" s="3" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="I446" s="3" t="s">
+      <x:c r="Q447" s="3" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="J446" s="3" t="s">
+      <x:c r="R447" s="3" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="K446" s="3" t="s">
+      <x:c r="S447" s="3" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="L446" s="3" t="s">
+      <x:c r="T447" s="3" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="M446" s="3" t="s">
+      <x:c r="U447" s="3" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="N446" s="3" t="s">
+      <x:c r="V447" s="3" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="O446" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="P446" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="Q446" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="R446" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="S446" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="T446" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="U446" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="V446" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V446"/>
+  <x:autoFilter ref="A1:V447"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -33204,39 +33278,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>791</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>792</x:v>
+        <x:v>794</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>793</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>794</x:v>
+        <x:v>796</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>795</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>796</x:v>
+        <x:v>798</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>797</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>445</x:v>
+        <x:v>446</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>798</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -33244,10 +33318,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>799</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>790</x:v>
+        <x:v>791</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
